--- a/downloads/exercises/intermedio-m03-m03-l05-practice-01.xlsx
+++ b/downloads/exercises/intermedio-m03-m03-l05-practice-01.xlsx
@@ -369,7 +369,7 @@
 123</x:v>
       </x:c>
       <x:c r="B7" t="str">
-        <x:v>Retorno de carro</x:v>
+        <x:v>Salto de línea</x:v>
       </x:c>
       <x:c r="C7" s="14"/>
       <x:c r="D7" s="14"/>
